--- a/data/trans_orig/IP07A15-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A15-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2007 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2007 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53364</t>
+          <t>53868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71511</t>
+          <t>73040</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50324</t>
+          <t>50097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69182</t>
+          <t>69105</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109827</t>
+          <t>109805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135527</t>
+          <t>135959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40541</t>
+          <t>39410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57930</t>
+          <t>57419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49623</t>
+          <t>49864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67737</t>
+          <t>68201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93759</t>
+          <t>94271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119942</t>
+          <t>120648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25169</t>
+          <t>25038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23923</t>
+          <t>24524</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41289</t>
+          <t>41328</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83784</t>
+          <t>84397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105600</t>
+          <t>106790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93185</t>
+          <t>93372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115957</t>
+          <t>115600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184780</t>
+          <t>184411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217208</t>
+          <t>214402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68468</t>
+          <t>68149</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91197</t>
+          <t>90229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69744</t>
+          <t>70455</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91457</t>
+          <t>91826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143432</t>
+          <t>146206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176232</t>
+          <t>175674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24505</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>25265</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>26418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44186</t>
+          <t>45029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145050</t>
+          <t>143320</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173446</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149774</t>
+          <t>149671</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>178783</t>
+          <t>177654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>303180</t>
+          <t>298946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>343844</t>
+          <t>341740</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113783</t>
+          <t>114229</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141400</t>
+          <t>142264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>123813</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154051</t>
+          <t>153391</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245882</t>
+          <t>247523</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286418</t>
+          <t>288973</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>39451</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>47264</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54807</t>
+          <t>54271</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81958</t>
+          <t>78720</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2012 (tasa de respuesta: 97,71%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2012 (tasa de respuesta: 97,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78969</t>
+          <t>78992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99732</t>
+          <t>99406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73265</t>
+          <t>73076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93597</t>
+          <t>93697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157858</t>
+          <t>157880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>189007</t>
+          <t>187372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43964</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64691</t>
+          <t>64717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47379</t>
+          <t>47813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67708</t>
+          <t>66944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96623</t>
+          <t>96953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123268</t>
+          <t>124829</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18042</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22711</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>19724</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35714</t>
+          <t>36596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74782</t>
+          <t>75508</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96618</t>
+          <t>96862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81986</t>
+          <t>82640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103093</t>
+          <t>103653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165852</t>
+          <t>164445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195406</t>
+          <t>193355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47150</t>
+          <t>47384</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67718</t>
+          <t>67227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54607</t>
+          <t>54108</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>74178</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107647</t>
+          <t>108523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135348</t>
+          <t>135645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30803</t>
+          <t>29738</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25713</t>
+          <t>26269</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43517</t>
+          <t>45041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>160192</t>
+          <t>158662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190536</t>
+          <t>189005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>161342</t>
+          <t>161523</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190949</t>
+          <t>190825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333256</t>
+          <t>332480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>373581</t>
+          <t>373666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95769</t>
+          <t>97487</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124692</t>
+          <t>124981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107400</t>
+          <t>108297</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137014</t>
+          <t>137129</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>212155</t>
+          <t>212380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252264</t>
+          <t>251701</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44483</t>
+          <t>42902</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>37770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50336</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74767</t>
+          <t>75043</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que los padres tubiesen suficiente tiempo par él/ella en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94867</t>
+          <t>95041</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117300</t>
+          <t>118387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93534</t>
+          <t>92181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116414</t>
+          <t>114931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>195222</t>
+          <t>196856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>226972</t>
+          <t>227078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48736</t>
+          <t>47882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69878</t>
+          <t>69259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54708</t>
+          <t>54258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75476</t>
+          <t>75844</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108467</t>
+          <t>108434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137875</t>
+          <t>137552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25463</t>
+          <t>25101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22152</t>
+          <t>22427</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>24971</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74816</t>
+          <t>74229</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96014</t>
+          <t>95375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79440</t>
+          <t>79011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102435</t>
+          <t>101689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191761</t>
+          <t>191341</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,71%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58954</t>
+          <t>58686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80035</t>
+          <t>79928</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57910</t>
+          <t>58484</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79954</t>
+          <t>80952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123679</t>
+          <t>123814</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153696</t>
+          <t>153432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32363</t>
+          <t>31934</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>177106</t>
+          <t>175656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>207296</t>
+          <t>207277</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180144</t>
+          <t>179935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>210791</t>
+          <t>209968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>365682</t>
+          <t>364597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>408658</t>
+          <t>408245</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,18%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114167</t>
+          <t>112328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143451</t>
+          <t>143418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118516</t>
+          <t>119256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148567</t>
+          <t>149030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>241959</t>
+          <t>240870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>282592</t>
+          <t>283003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22740</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41149</t>
+          <t>40988</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44993</t>
+          <t>45085</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68704</t>
+          <t>68805</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A15-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A15-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2007 (tasa de respuesta: 98,9%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59369</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50169</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>69345</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>62746</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>53868</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>73040</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>53556</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>71530</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,45%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>59369</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>50097</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>69105</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,73%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109805</t>
+          <t>108224</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135959</t>
+          <t>136177</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59210</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49709</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68220</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48215</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>39410</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57419</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40044</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>57454</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,25%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59210</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>49864</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68201</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>42,62%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94271</t>
+          <t>95200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120648</t>
+          <t>121337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18236</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12323</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24698</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>13973</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9281</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20582</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9340</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>19982</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>11,01%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18236</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12589</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>25038</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24524</t>
+          <t>24422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41328</t>
+          <t>41187</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4944</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1960</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5823</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5025</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4476</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>635</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3499</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>138936</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>138936</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>138936</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>138936</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>138936</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>138936</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>104319</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>93078</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>116185</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>95430</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>84397</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>106790</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>85246</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>107070</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,86%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>104319</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>93372</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>115600</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>51,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184411</t>
+          <t>182759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214402</t>
+          <t>215220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,36%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>80398</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69251</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>91346</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>79540</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>68149</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>90229</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>67656</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>89297</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>41,34%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>80398</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>70455</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>91826</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146206</t>
+          <t>145136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175674</t>
+          <t>176448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18079</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11988</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>25841</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>16908</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11223</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24676</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10917</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>23700</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,79%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18079</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12031</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>25265</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26418</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45029</t>
+          <t>45570</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -1743,107 +1743,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3127</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3424</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3245</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>537</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3257</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3116</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2692</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>537</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3427</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203475</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203475</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203475</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192415</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192415</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192415</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203475</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203475</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203475</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,107 +2086,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>163687</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>148513</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>177965</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>158176</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>143320</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>172100</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>144658</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>173228</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>49,54%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>163687</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>149671</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>177654</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>47,8%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>54,25%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>321863</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>301312</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>343329</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>48,64%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>45,53%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>51,88%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>321863</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>298946</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>341740</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>48,64%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>45,18%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139608</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>125776</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>155540</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>127755</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>114229</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>142264</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>113532</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>141624</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>40,01%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139608</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123813</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>153391</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247523</t>
+          <t>247983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288973</t>
+          <t>288109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>36315</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>28440</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46529</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>30881</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>22370</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>39451</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>22661</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>39760</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>9,67%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>36315</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>27856</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>47264</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54271</t>
+          <t>55984</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78720</t>
+          <t>80199</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -2430,67 +2430,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>2165</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6052</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>1960</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5281</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2165</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5826</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2543,102 +2543,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3179</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2861</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2567</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4145</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1171</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4114</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>342410</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>342410</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>342410</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>319309</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>319309</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>319309</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>342410</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>342410</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>342410</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2012 (tasa de respuesta: 97,71%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>83709</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>72494</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>93709</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>46,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>59,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>88994</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>78992</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>99406</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>78300</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>98649</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>83709</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>73076</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>93697</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>53,43%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157880</t>
+          <t>157633</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>187372</t>
+          <t>187010</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,9%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57171</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47925</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68247</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53329</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43464</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64717</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43176</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>63820</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>34,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,95%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57171</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>47813</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66944</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,49%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96953</t>
+          <t>96399</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124829</t>
+          <t>125194</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15230</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9853</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22620</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,44%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11664</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6802</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17629</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6900</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>18044</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,5%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9849</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22569</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,72%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36596</t>
+          <t>36404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1528</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5815</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5395</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2878</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>92877</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>81335</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>103233</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>46,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>59,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>86305</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>75508</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>96862</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>75575</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>97062</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>92877</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>82640</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>103653</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>53,51%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164445</t>
+          <t>164364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193355</t>
+          <t>193807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,12%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64498</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54340</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75285</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>57291</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>47384</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>67227</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>46993</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>68226</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>34,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>64498</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>54108</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74178</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,16%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108523</t>
+          <t>106446</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135645</t>
+          <t>135200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13240</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8175</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19693</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>21469</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14258</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29738</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>15218</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>30184</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>12,95%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>13240</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8633</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>20436</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26269</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45041</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6195</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3200</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2192</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6224</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -4132,92 +4132,92 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>767</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4136</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173574</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173574</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173574</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165744</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165744</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165744</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173574</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173574</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173574</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>176586</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>161346</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>191546</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53,47%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>48,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>175299</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>158662</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>189005</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>161330</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>190904</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>54,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,39%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>176586</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>161523</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>190825</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>53,47%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>332480</t>
+          <t>330765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>373666</t>
+          <t>372783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>121669</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>108197</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>137893</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,84%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,75%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>110619</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>97487</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>124981</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>96928</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>124177</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>121669</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>108297</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>137129</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,84%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>212380</t>
+          <t>211895</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251701</t>
+          <t>252490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>28471</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>21159</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>38004</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>33133</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>24994</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>42902</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>24287</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>42667</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>10,31%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>28471</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>20481</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>37770</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50029</t>
+          <t>50554</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75043</t>
+          <t>75573</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2756</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2206</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>611</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6048</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2756</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6670</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4814,92 +4814,92 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4640</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>767</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>3832</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>330248</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>330248</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>330248</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321258</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321258</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321258</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>330248</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>330248</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>330248</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de que los padres tuviesen suficiente tiempo par él/ella, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>104820</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>93084</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>115610</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>56,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>106630</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>95041</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>118387</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>95480</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>117952</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>104820</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>92181</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>114931</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>56,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>196856</t>
+          <t>194543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227078</t>
+          <t>227306</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64536</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53428</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>75614</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58615</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47882</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>69259</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47634</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>69662</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,65%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64536</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>54258</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>75844</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108434</t>
+          <t>107183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137552</t>
+          <t>137857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15257</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9579</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22262</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,01%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18043</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11604</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25101</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>11888</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>25328</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>9,74%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15257</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9782</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22427</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>25379</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42752</t>
+          <t>43993</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3562</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1895</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5291</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4286</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>185321</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>185321</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>185321</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>185321</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>185321</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>185321</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90506</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>78369</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>101769</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>85240</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>74229</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>95375</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>74000</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>95390</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>50,11%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,64%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>90506</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>79011</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>101689</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>52,22%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160799</t>
+          <t>158831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191341</t>
+          <t>191172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,66%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69195</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>58066</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81222</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>69541</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58686</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>79928</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>58906</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>79747</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69195</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>58484</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>80952</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,92%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123814</t>
+          <t>124191</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153432</t>
+          <t>155050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10474</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5923</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17691</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>12453</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7514</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19602</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7438</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20025</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,32%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10474</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6116</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>17281</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31934</t>
+          <t>31574</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -6300,67 +6300,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3155</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7744</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2868</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7042</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8291</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8211</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173330</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173330</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173330</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170102</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170102</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170102</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173330</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173330</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173330</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>195326</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>180504</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>211427</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,46%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>50,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>191871</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>175656</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>207277</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>176381</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>207509</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>54,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>195326</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>179935</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>209968</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>54,46%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>364597</t>
+          <t>366765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>408245</t>
+          <t>407943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>133731</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>118154</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>148493</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>128156</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>112328</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>143418</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>111494</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>143362</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>36,07%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,37%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>133731</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>119256</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>149030</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,29%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>240870</t>
+          <t>241330</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283003</t>
+          <t>284137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>35023</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>30496</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>22816</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>40988</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>22255</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>40487</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,58%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>25731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>18012</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>34353</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45085</t>
+          <t>45132</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68805</t>
+          <t>69520</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3864</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8833</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>4763</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2162</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9952</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1872</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>9716</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,34%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3864</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8806</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>358652</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>358652</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>358652</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>508</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>355286</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>355286</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>355286</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>358652</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>358652</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>358652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
